--- a/data/AT_20260520_V3_Claude.xlsx
+++ b/data/AT_20260520_V3_Claude.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\20260905-remigration-institute\20260524-sheet-analysis\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\20260905-ifr\20260509-plausibility-analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_9126833E5D45B67F39ACB57430632C40A19F6108" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="19695" windowHeight="13740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overview" sheetId="1" r:id="rId1"/>
@@ -5735,17 +5735,32 @@
     <xf numFmtId="1" fontId="0" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
@@ -5757,19 +5772,13 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="5" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5778,15 +5787,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5805,13 +5805,13 @@
     <xf numFmtId="49" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6957,20 +6957,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="174" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
+      <c r="A1" s="181" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -7082,65 +7082,65 @@
       <c r="B5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="191" t="s">
+      <c r="C5" s="194" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="175"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="175"/>
-      <c r="G5" s="175"/>
-      <c r="H5" s="175"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="175"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="179"/>
+      <c r="G5" s="179"/>
+      <c r="H5" s="179"/>
+      <c r="I5" s="179"/>
+      <c r="J5" s="179"/>
+      <c r="K5" s="179"/>
       <c r="L5" s="13"/>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="14"/>
-      <c r="C6" s="190" t="s">
+      <c r="C6" s="193" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="175"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="175"/>
-      <c r="G6" s="175"/>
-      <c r="H6" s="175"/>
-      <c r="I6" s="175"/>
-      <c r="J6" s="175"/>
-      <c r="K6" s="175"/>
+      <c r="D6" s="179"/>
+      <c r="E6" s="179"/>
+      <c r="F6" s="179"/>
+      <c r="G6" s="179"/>
+      <c r="H6" s="179"/>
+      <c r="I6" s="179"/>
+      <c r="J6" s="179"/>
+      <c r="K6" s="179"/>
       <c r="L6" s="13"/>
     </row>
     <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="14"/>
-      <c r="C7" s="189" t="s">
+      <c r="C7" s="192" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="175"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
-      <c r="I7" s="175"/>
-      <c r="J7" s="175"/>
-      <c r="K7" s="175"/>
+      <c r="D7" s="179"/>
+      <c r="E7" s="179"/>
+      <c r="F7" s="179"/>
+      <c r="G7" s="179"/>
+      <c r="H7" s="179"/>
+      <c r="I7" s="179"/>
+      <c r="J7" s="179"/>
+      <c r="K7" s="179"/>
       <c r="L7" s="13"/>
     </row>
     <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="15"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="187" t="s">
+      <c r="C8" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="188"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="188"/>
-      <c r="G8" s="188"/>
-      <c r="H8" s="188"/>
-      <c r="I8" s="188"/>
-      <c r="J8" s="188"/>
-      <c r="K8" s="188"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177"/>
+      <c r="G8" s="177"/>
+      <c r="H8" s="177"/>
+      <c r="I8" s="177"/>
+      <c r="J8" s="177"/>
+      <c r="K8" s="177"/>
       <c r="L8" s="13"/>
     </row>
     <row r="9" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7162,15 +7162,15 @@
       <c r="B10" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="178"/>
-      <c r="D10" s="177"/>
-      <c r="E10" s="177"/>
-      <c r="F10" s="177"/>
-      <c r="G10" s="177"/>
-      <c r="H10" s="177"/>
-      <c r="I10" s="177"/>
-      <c r="J10" s="177"/>
-      <c r="K10" s="177"/>
+      <c r="C10" s="190"/>
+      <c r="D10" s="175"/>
+      <c r="E10" s="175"/>
+      <c r="F10" s="175"/>
+      <c r="G10" s="175"/>
+      <c r="H10" s="175"/>
+      <c r="I10" s="175"/>
+      <c r="J10" s="175"/>
+      <c r="K10" s="175"/>
       <c r="L10" s="22"/>
     </row>
     <row r="11" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7180,17 +7180,17 @@
       <c r="B11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="176" t="s">
+      <c r="C11" s="189" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="177"/>
-      <c r="E11" s="177"/>
-      <c r="F11" s="177"/>
-      <c r="G11" s="177"/>
-      <c r="H11" s="177"/>
-      <c r="I11" s="177"/>
-      <c r="J11" s="177"/>
-      <c r="K11" s="177"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="175"/>
+      <c r="F11" s="175"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="175"/>
+      <c r="I11" s="175"/>
+      <c r="J11" s="175"/>
+      <c r="K11" s="175"/>
       <c r="L11" s="13"/>
     </row>
     <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7200,17 +7200,17 @@
       <c r="B12" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="176" t="s">
+      <c r="C12" s="189" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="177"/>
-      <c r="E12" s="177"/>
-      <c r="F12" s="177"/>
-      <c r="G12" s="177"/>
-      <c r="H12" s="177"/>
-      <c r="I12" s="177"/>
-      <c r="J12" s="177"/>
-      <c r="K12" s="177"/>
+      <c r="D12" s="175"/>
+      <c r="E12" s="175"/>
+      <c r="F12" s="175"/>
+      <c r="G12" s="175"/>
+      <c r="H12" s="175"/>
+      <c r="I12" s="175"/>
+      <c r="J12" s="175"/>
+      <c r="K12" s="175"/>
       <c r="L12" s="13"/>
     </row>
     <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7220,17 +7220,17 @@
       <c r="B13" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="176" t="s">
+      <c r="C13" s="189" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="177"/>
-      <c r="E13" s="177"/>
-      <c r="F13" s="177"/>
-      <c r="G13" s="177"/>
-      <c r="H13" s="177"/>
-      <c r="I13" s="177"/>
-      <c r="J13" s="177"/>
-      <c r="K13" s="177"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="175"/>
+      <c r="F13" s="175"/>
+      <c r="G13" s="175"/>
+      <c r="H13" s="175"/>
+      <c r="I13" s="175"/>
+      <c r="J13" s="175"/>
+      <c r="K13" s="175"/>
       <c r="L13" s="13"/>
     </row>
     <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7252,17 +7252,17 @@
       <c r="B15" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="179" t="s">
+      <c r="C15" s="184" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="177"/>
-      <c r="E15" s="177"/>
-      <c r="F15" s="177"/>
-      <c r="G15" s="177"/>
-      <c r="H15" s="177"/>
-      <c r="I15" s="177"/>
-      <c r="J15" s="177"/>
-      <c r="K15" s="177"/>
+      <c r="D15" s="175"/>
+      <c r="E15" s="175"/>
+      <c r="F15" s="175"/>
+      <c r="G15" s="175"/>
+      <c r="H15" s="175"/>
+      <c r="I15" s="175"/>
+      <c r="J15" s="175"/>
+      <c r="K15" s="175"/>
       <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7292,11 +7292,11 @@
         <f t="array" ref="D17">C34</f>
         <v>0.28226311601133952</v>
       </c>
-      <c r="E17" s="180" t="s">
+      <c r="E17" s="185" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="175"/>
-      <c r="G17" s="175"/>
+      <c r="F17" s="179"/>
+      <c r="G17" s="179"/>
       <c r="H17" s="29">
         <f t="array" ref="H17">population!H109</f>
         <v>6601179</v>
@@ -7381,12 +7381,12 @@
         <v>45</v>
       </c>
       <c r="C21" s="12"/>
-      <c r="D21" s="180" t="s">
+      <c r="D21" s="185" t="s">
         <v>46</v>
       </c>
-      <c r="E21" s="175"/>
-      <c r="F21" s="175"/>
-      <c r="G21" s="175"/>
+      <c r="E21" s="179"/>
+      <c r="F21" s="179"/>
+      <c r="G21" s="179"/>
       <c r="H21" s="29">
         <f t="array" ref="H21">IF(ISNUMBER(H20),H20,H19)</f>
         <v>43896.0408837168</v>
@@ -7456,11 +7456,11 @@
         <f t="array" ref="D24">C24/C17</f>
         <v>1.3381653576204706E-2</v>
       </c>
-      <c r="E24" s="180" t="s">
+      <c r="E24" s="185" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="175"/>
-      <c r="G24" s="175"/>
+      <c r="F24" s="179"/>
+      <c r="G24" s="179"/>
       <c r="H24" s="29">
         <f t="array" ref="H24">H21+H22+H23</f>
         <v>-35921.4591162832</v>
@@ -7496,12 +7496,12 @@
         <f t="array" ref="C26">(H$17-2*I$17)/(2*I$24-H$24)</f>
         <v>6.7028268182623032</v>
       </c>
-      <c r="D26" s="183" t="s">
+      <c r="D26" s="188" t="s">
         <v>52</v>
       </c>
-      <c r="E26" s="175"/>
-      <c r="F26" s="175"/>
-      <c r="G26" s="175"/>
+      <c r="E26" s="179"/>
+      <c r="F26" s="179"/>
+      <c r="G26" s="179"/>
       <c r="H26" s="13"/>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
@@ -7536,12 +7536,12 @@
         <f t="array" ref="C28">(H$17-I$17)/(I$24-H$24)</f>
         <v>32.542597631706862</v>
       </c>
-      <c r="D28" s="183" t="s">
+      <c r="D28" s="188" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="175"/>
-      <c r="F28" s="175"/>
-      <c r="G28" s="175"/>
+      <c r="E28" s="179"/>
+      <c r="F28" s="179"/>
+      <c r="G28" s="179"/>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
@@ -7586,17 +7586,17 @@
       <c r="B31" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="179" t="s">
+      <c r="C31" s="184" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="177"/>
-      <c r="E31" s="177"/>
-      <c r="F31" s="177"/>
-      <c r="G31" s="177"/>
-      <c r="H31" s="177"/>
-      <c r="I31" s="177"/>
-      <c r="J31" s="177"/>
-      <c r="K31" s="177"/>
+      <c r="D31" s="175"/>
+      <c r="E31" s="175"/>
+      <c r="F31" s="175"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="175"/>
+      <c r="I31" s="175"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="175"/>
       <c r="L31" s="22"/>
     </row>
     <row r="32" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7641,12 +7641,12 @@
         <f t="array" ref="C34">population!I109/population!C109</f>
         <v>0.28226311601133952</v>
       </c>
-      <c r="D34" s="181" t="s">
+      <c r="D34" s="186" t="s">
         <v>61</v>
       </c>
-      <c r="E34" s="182"/>
-      <c r="F34" s="182"/>
-      <c r="G34" s="182"/>
+      <c r="E34" s="187"/>
+      <c r="F34" s="187"/>
+      <c r="G34" s="187"/>
       <c r="H34" s="13"/>
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
@@ -7662,12 +7662,12 @@
         <f t="array" ref="C35">I35/H35-1</f>
         <v>0.29769736842105288</v>
       </c>
-      <c r="D35" s="183" t="s">
+      <c r="D35" s="188" t="s">
         <v>63</v>
       </c>
-      <c r="E35" s="175"/>
-      <c r="F35" s="175"/>
-      <c r="G35" s="175"/>
+      <c r="E35" s="179"/>
+      <c r="F35" s="179"/>
+      <c r="G35" s="179"/>
       <c r="H35" s="36">
         <f t="array" ref="H35">births!H11/births!D9*1000000</f>
         <v>34735.575035385053</v>
@@ -7689,12 +7689,12 @@
         <f t="array" ref="C36">I36/H36-1</f>
         <v>0.8426756316239794</v>
       </c>
-      <c r="D36" s="183" t="s">
+      <c r="D36" s="188" t="s">
         <v>65</v>
       </c>
-      <c r="E36" s="175"/>
-      <c r="F36" s="175"/>
-      <c r="G36" s="175"/>
+      <c r="E36" s="179"/>
+      <c r="F36" s="179"/>
+      <c r="G36" s="179"/>
       <c r="H36" s="27">
         <f t="array" ref="H36">births!H11/population!H109*1000000</f>
         <v>6649.727402289318</v>
@@ -7716,12 +7716,12 @@
         <f t="array" ref="C37">I37/H37-1</f>
         <v>-0.46298418234357563</v>
       </c>
-      <c r="D37" s="183" t="s">
+      <c r="D37" s="188" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="175"/>
-      <c r="F37" s="175"/>
-      <c r="G37" s="175"/>
+      <c r="E37" s="179"/>
+      <c r="F37" s="179"/>
+      <c r="G37" s="179"/>
       <c r="H37" s="27">
         <f t="array" ref="H37">deaths!H$107/population!H$109*1000000</f>
         <v>11067.265408194506</v>
@@ -7881,17 +7881,17 @@
       <c r="B47" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="C47" s="179" t="s">
+      <c r="C47" s="184" t="s">
         <v>71</v>
       </c>
-      <c r="D47" s="177"/>
-      <c r="E47" s="177"/>
-      <c r="F47" s="177"/>
-      <c r="G47" s="177"/>
-      <c r="H47" s="177"/>
-      <c r="I47" s="177"/>
-      <c r="J47" s="177"/>
-      <c r="K47" s="177"/>
+      <c r="D47" s="175"/>
+      <c r="E47" s="175"/>
+      <c r="F47" s="175"/>
+      <c r="G47" s="175"/>
+      <c r="H47" s="175"/>
+      <c r="I47" s="175"/>
+      <c r="J47" s="175"/>
+      <c r="K47" s="175"/>
       <c r="L47" s="22"/>
     </row>
     <row r="48" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7915,17 +7915,17 @@
       <c r="B49" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C49" s="186" t="s">
+      <c r="C49" s="174" t="s">
         <v>74</v>
       </c>
-      <c r="D49" s="177"/>
-      <c r="E49" s="177"/>
-      <c r="F49" s="177"/>
-      <c r="G49" s="177"/>
-      <c r="H49" s="177"/>
-      <c r="I49" s="177"/>
-      <c r="J49" s="177"/>
-      <c r="K49" s="177"/>
+      <c r="D49" s="175"/>
+      <c r="E49" s="175"/>
+      <c r="F49" s="175"/>
+      <c r="G49" s="175"/>
+      <c r="H49" s="175"/>
+      <c r="I49" s="175"/>
+      <c r="J49" s="175"/>
+      <c r="K49" s="175"/>
       <c r="L49" s="13"/>
     </row>
     <row r="50" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7949,18 +7949,18 @@
       <c r="B51" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="184" t="str">
+      <c r="C51" s="182" t="str">
         <f t="array" ref="C51">IF(C52="","?",C52)&amp;IF(C53="","","; downloaded "&amp;C53)&amp;IF(C54="","","; "&amp;C54)</f>
         <v>https://www.statistik.at/statistiken/bevoelkerung-und-soziales/bevoelkerung/migration-und-einbuergerung/migrationshintergrund, https://www.statistik.at/fileadmin/pages/435/Tabellensammlung_Migrationshintergrund_2025.ods, https://www.statistik.at/fileadmin/publications/Migration-Integration_2025.pdf; downloaded 2026-05-20</v>
       </c>
-      <c r="D51" s="177"/>
-      <c r="E51" s="177"/>
-      <c r="F51" s="177"/>
-      <c r="G51" s="177"/>
-      <c r="H51" s="177"/>
-      <c r="I51" s="177"/>
-      <c r="J51" s="177"/>
-      <c r="K51" s="177"/>
+      <c r="D51" s="175"/>
+      <c r="E51" s="175"/>
+      <c r="F51" s="175"/>
+      <c r="G51" s="175"/>
+      <c r="H51" s="175"/>
+      <c r="I51" s="175"/>
+      <c r="J51" s="175"/>
+      <c r="K51" s="175"/>
       <c r="L51" s="13"/>
     </row>
     <row r="52" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7968,17 +7968,17 @@
       <c r="B52" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="185" t="s">
+      <c r="C52" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="D52" s="177"/>
-      <c r="E52" s="177"/>
-      <c r="F52" s="177"/>
-      <c r="G52" s="177"/>
-      <c r="H52" s="177"/>
-      <c r="I52" s="177"/>
-      <c r="J52" s="177"/>
-      <c r="K52" s="177"/>
+      <c r="D52" s="175"/>
+      <c r="E52" s="175"/>
+      <c r="F52" s="175"/>
+      <c r="G52" s="175"/>
+      <c r="H52" s="175"/>
+      <c r="I52" s="175"/>
+      <c r="J52" s="175"/>
+      <c r="K52" s="175"/>
       <c r="L52" s="13"/>
     </row>
     <row r="53" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -7986,17 +7986,17 @@
       <c r="B53" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C53" s="185" t="s">
+      <c r="C53" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="D53" s="177"/>
-      <c r="E53" s="177"/>
-      <c r="F53" s="177"/>
-      <c r="G53" s="177"/>
-      <c r="H53" s="177"/>
-      <c r="I53" s="177"/>
-      <c r="J53" s="177"/>
-      <c r="K53" s="177"/>
+      <c r="D53" s="175"/>
+      <c r="E53" s="175"/>
+      <c r="F53" s="175"/>
+      <c r="G53" s="175"/>
+      <c r="H53" s="175"/>
+      <c r="I53" s="175"/>
+      <c r="J53" s="175"/>
+      <c r="K53" s="175"/>
       <c r="L53" s="13"/>
     </row>
     <row r="54" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8004,15 +8004,15 @@
       <c r="B54" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="186"/>
-      <c r="D54" s="177"/>
-      <c r="E54" s="177"/>
-      <c r="F54" s="177"/>
-      <c r="G54" s="177"/>
-      <c r="H54" s="177"/>
-      <c r="I54" s="177"/>
-      <c r="J54" s="177"/>
-      <c r="K54" s="177"/>
+      <c r="C54" s="174"/>
+      <c r="D54" s="175"/>
+      <c r="E54" s="175"/>
+      <c r="F54" s="175"/>
+      <c r="G54" s="175"/>
+      <c r="H54" s="175"/>
+      <c r="I54" s="175"/>
+      <c r="J54" s="175"/>
+      <c r="K54" s="175"/>
       <c r="L54" s="13"/>
     </row>
     <row r="55" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8020,17 +8020,17 @@
       <c r="B55" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C55" s="186" t="s">
+      <c r="C55" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="D55" s="177"/>
-      <c r="E55" s="177"/>
-      <c r="F55" s="177"/>
-      <c r="G55" s="177"/>
-      <c r="H55" s="177"/>
-      <c r="I55" s="177"/>
-      <c r="J55" s="177"/>
-      <c r="K55" s="177"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="175"/>
+      <c r="G55" s="175"/>
+      <c r="H55" s="175"/>
+      <c r="I55" s="175"/>
+      <c r="J55" s="175"/>
+      <c r="K55" s="175"/>
       <c r="L55" s="13"/>
     </row>
     <row r="56" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8038,15 +8038,15 @@
       <c r="B56" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C56" s="186"/>
-      <c r="D56" s="177"/>
-      <c r="E56" s="177"/>
-      <c r="F56" s="177"/>
-      <c r="G56" s="177"/>
-      <c r="H56" s="177"/>
-      <c r="I56" s="177"/>
-      <c r="J56" s="177"/>
-      <c r="K56" s="177"/>
+      <c r="C56" s="174"/>
+      <c r="D56" s="175"/>
+      <c r="E56" s="175"/>
+      <c r="F56" s="175"/>
+      <c r="G56" s="175"/>
+      <c r="H56" s="175"/>
+      <c r="I56" s="175"/>
+      <c r="J56" s="175"/>
+      <c r="K56" s="175"/>
       <c r="L56" s="13"/>
     </row>
     <row r="57" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8068,17 +8068,17 @@
       <c r="B58" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C58" s="179" t="s">
+      <c r="C58" s="184" t="s">
         <v>86</v>
       </c>
-      <c r="D58" s="177"/>
-      <c r="E58" s="177"/>
-      <c r="F58" s="177"/>
-      <c r="G58" s="177"/>
-      <c r="H58" s="177"/>
-      <c r="I58" s="177"/>
-      <c r="J58" s="177"/>
-      <c r="K58" s="177"/>
+      <c r="D58" s="175"/>
+      <c r="E58" s="175"/>
+      <c r="F58" s="175"/>
+      <c r="G58" s="175"/>
+      <c r="H58" s="175"/>
+      <c r="I58" s="175"/>
+      <c r="J58" s="175"/>
+      <c r="K58" s="175"/>
       <c r="L58" s="22"/>
     </row>
     <row r="59" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8157,18 +8157,18 @@
       <c r="B62" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="184" t="str">
+      <c r="C62" s="182" t="str">
         <f t="array" ref="C62">IF(C63="","?",C63)&amp;IF(C64="","","; downloaded "&amp;C64)&amp;IF(C65="","","; "&amp;C65)</f>
         <v>https://www.statistik.at/fileadmin/pages/413/Sterbetafel_2024_fuer_Oesterreich.ods; downloaded 2026-05-20</v>
       </c>
-      <c r="D62" s="177"/>
-      <c r="E62" s="177"/>
-      <c r="F62" s="177"/>
-      <c r="G62" s="177"/>
-      <c r="H62" s="177"/>
-      <c r="I62" s="177"/>
-      <c r="J62" s="177"/>
-      <c r="K62" s="177"/>
+      <c r="D62" s="175"/>
+      <c r="E62" s="175"/>
+      <c r="F62" s="175"/>
+      <c r="G62" s="175"/>
+      <c r="H62" s="175"/>
+      <c r="I62" s="175"/>
+      <c r="J62" s="175"/>
+      <c r="K62" s="175"/>
       <c r="L62" s="13"/>
     </row>
     <row r="63" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8176,17 +8176,17 @@
       <c r="B63" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="185" t="s">
+      <c r="C63" s="183" t="s">
         <v>90</v>
       </c>
-      <c r="D63" s="177"/>
-      <c r="E63" s="177"/>
-      <c r="F63" s="177"/>
-      <c r="G63" s="177"/>
-      <c r="H63" s="177"/>
-      <c r="I63" s="177"/>
-      <c r="J63" s="177"/>
-      <c r="K63" s="177"/>
+      <c r="D63" s="175"/>
+      <c r="E63" s="175"/>
+      <c r="F63" s="175"/>
+      <c r="G63" s="175"/>
+      <c r="H63" s="175"/>
+      <c r="I63" s="175"/>
+      <c r="J63" s="175"/>
+      <c r="K63" s="175"/>
       <c r="L63" s="13"/>
     </row>
     <row r="64" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8194,17 +8194,17 @@
       <c r="B64" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C64" s="185" t="s">
+      <c r="C64" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="D64" s="177"/>
-      <c r="E64" s="177"/>
-      <c r="F64" s="177"/>
-      <c r="G64" s="177"/>
-      <c r="H64" s="177"/>
-      <c r="I64" s="177"/>
-      <c r="J64" s="177"/>
-      <c r="K64" s="177"/>
+      <c r="D64" s="175"/>
+      <c r="E64" s="175"/>
+      <c r="F64" s="175"/>
+      <c r="G64" s="175"/>
+      <c r="H64" s="175"/>
+      <c r="I64" s="175"/>
+      <c r="J64" s="175"/>
+      <c r="K64" s="175"/>
       <c r="L64" s="13"/>
     </row>
     <row r="65" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8212,15 +8212,15 @@
       <c r="B65" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C65" s="186"/>
-      <c r="D65" s="177"/>
-      <c r="E65" s="177"/>
-      <c r="F65" s="177"/>
-      <c r="G65" s="177"/>
-      <c r="H65" s="177"/>
-      <c r="I65" s="177"/>
-      <c r="J65" s="177"/>
-      <c r="K65" s="177"/>
+      <c r="C65" s="174"/>
+      <c r="D65" s="175"/>
+      <c r="E65" s="175"/>
+      <c r="F65" s="175"/>
+      <c r="G65" s="175"/>
+      <c r="H65" s="175"/>
+      <c r="I65" s="175"/>
+      <c r="J65" s="175"/>
+      <c r="K65" s="175"/>
       <c r="L65" s="13"/>
     </row>
     <row r="66" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8228,17 +8228,17 @@
       <c r="B66" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C66" s="186" t="s">
+      <c r="C66" s="174" t="s">
         <v>91</v>
       </c>
-      <c r="D66" s="177"/>
-      <c r="E66" s="177"/>
-      <c r="F66" s="177"/>
-      <c r="G66" s="177"/>
-      <c r="H66" s="177"/>
-      <c r="I66" s="177"/>
-      <c r="J66" s="177"/>
-      <c r="K66" s="177"/>
+      <c r="D66" s="175"/>
+      <c r="E66" s="175"/>
+      <c r="F66" s="175"/>
+      <c r="G66" s="175"/>
+      <c r="H66" s="175"/>
+      <c r="I66" s="175"/>
+      <c r="J66" s="175"/>
+      <c r="K66" s="175"/>
       <c r="L66" s="13"/>
     </row>
     <row r="67" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8246,15 +8246,15 @@
       <c r="B67" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C67" s="186"/>
-      <c r="D67" s="177"/>
-      <c r="E67" s="177"/>
-      <c r="F67" s="177"/>
-      <c r="G67" s="177"/>
-      <c r="H67" s="177"/>
-      <c r="I67" s="177"/>
-      <c r="J67" s="177"/>
-      <c r="K67" s="177"/>
+      <c r="C67" s="174"/>
+      <c r="D67" s="175"/>
+      <c r="E67" s="175"/>
+      <c r="F67" s="175"/>
+      <c r="G67" s="175"/>
+      <c r="H67" s="175"/>
+      <c r="I67" s="175"/>
+      <c r="J67" s="175"/>
+      <c r="K67" s="175"/>
       <c r="L67" s="13"/>
     </row>
     <row r="68" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -8273,6 +8273,27 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C11:K11"/>
+    <mergeCell ref="C12:K12"/>
+    <mergeCell ref="C10:K10"/>
+    <mergeCell ref="C31:K31"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="C7:K7"/>
+    <mergeCell ref="C6:K6"/>
+    <mergeCell ref="C5:K5"/>
+    <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C47:K47"/>
+    <mergeCell ref="C15:K15"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D28:G28"/>
     <mergeCell ref="C67:K67"/>
     <mergeCell ref="C49:K49"/>
     <mergeCell ref="C51:K51"/>
@@ -8287,27 +8308,6 @@
     <mergeCell ref="C63:K63"/>
     <mergeCell ref="C64:K64"/>
     <mergeCell ref="C65:K65"/>
-    <mergeCell ref="C47:K47"/>
-    <mergeCell ref="C15:K15"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C11:K11"/>
-    <mergeCell ref="C12:K12"/>
-    <mergeCell ref="C10:K10"/>
-    <mergeCell ref="C31:K31"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="C7:K7"/>
-    <mergeCell ref="C6:K6"/>
-    <mergeCell ref="C5:K5"/>
-    <mergeCell ref="C13:K13"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -8332,20 +8332,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="181" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -8421,17 +8421,17 @@
       <c r="B4" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="193" t="s">
+      <c r="C4" s="178" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="175"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="179"/>
+      <c r="I4" s="179"/>
+      <c r="J4" s="179"/>
+      <c r="K4" s="179"/>
       <c r="L4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="26.85" customHeight="1">
@@ -8439,17 +8439,17 @@
       <c r="B5" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="176" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="188"/>
-      <c r="K5" s="188"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
       <c r="L5" s="22"/>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13066,18 +13066,18 @@
       <c r="B111" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C111" s="184" t="str">
+      <c r="C111" s="182" t="str">
         <f t="array" ref="C111">IF(C112="","?",C112)&amp;IF(C113="","","; downloaded "&amp;C113)&amp;IF(C114="","","; "&amp;C114)</f>
         <v>https://data.statistik.gv.at/data/OGD_bevstandjbab2002_BevStand_2025.csv, https://www.statistik.at/fileadmin/pages/435/Tabellensammlung_Migrationshintergrund_2025.ods; downloaded 2026-05-20</v>
       </c>
-      <c r="D111" s="177"/>
-      <c r="E111" s="177"/>
-      <c r="F111" s="177"/>
-      <c r="G111" s="177"/>
-      <c r="H111" s="177"/>
-      <c r="I111" s="177"/>
-      <c r="J111" s="177"/>
-      <c r="K111" s="177"/>
+      <c r="D111" s="175"/>
+      <c r="E111" s="175"/>
+      <c r="F111" s="175"/>
+      <c r="G111" s="175"/>
+      <c r="H111" s="175"/>
+      <c r="I111" s="175"/>
+      <c r="J111" s="175"/>
+      <c r="K111" s="175"/>
       <c r="L111" s="13"/>
     </row>
     <row r="112" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13085,17 +13085,17 @@
       <c r="B112" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C112" s="185" t="s">
+      <c r="C112" s="183" t="s">
         <v>302</v>
       </c>
-      <c r="D112" s="177"/>
-      <c r="E112" s="177"/>
-      <c r="F112" s="177"/>
-      <c r="G112" s="177"/>
-      <c r="H112" s="177"/>
-      <c r="I112" s="177"/>
-      <c r="J112" s="177"/>
-      <c r="K112" s="177"/>
+      <c r="D112" s="175"/>
+      <c r="E112" s="175"/>
+      <c r="F112" s="175"/>
+      <c r="G112" s="175"/>
+      <c r="H112" s="175"/>
+      <c r="I112" s="175"/>
+      <c r="J112" s="175"/>
+      <c r="K112" s="175"/>
       <c r="L112" s="13"/>
     </row>
     <row r="113" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13103,17 +13103,17 @@
       <c r="B113" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C113" s="185" t="s">
+      <c r="C113" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="D113" s="177"/>
-      <c r="E113" s="177"/>
-      <c r="F113" s="177"/>
-      <c r="G113" s="177"/>
-      <c r="H113" s="177"/>
-      <c r="I113" s="177"/>
-      <c r="J113" s="177"/>
-      <c r="K113" s="177"/>
+      <c r="D113" s="175"/>
+      <c r="E113" s="175"/>
+      <c r="F113" s="175"/>
+      <c r="G113" s="175"/>
+      <c r="H113" s="175"/>
+      <c r="I113" s="175"/>
+      <c r="J113" s="175"/>
+      <c r="K113" s="175"/>
       <c r="L113" s="13"/>
     </row>
     <row r="114" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13121,15 +13121,15 @@
       <c r="B114" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C114" s="186"/>
-      <c r="D114" s="177"/>
-      <c r="E114" s="177"/>
-      <c r="F114" s="177"/>
-      <c r="G114" s="177"/>
-      <c r="H114" s="177"/>
-      <c r="I114" s="177"/>
-      <c r="J114" s="177"/>
-      <c r="K114" s="177"/>
+      <c r="C114" s="174"/>
+      <c r="D114" s="175"/>
+      <c r="E114" s="175"/>
+      <c r="F114" s="175"/>
+      <c r="G114" s="175"/>
+      <c r="H114" s="175"/>
+      <c r="I114" s="175"/>
+      <c r="J114" s="175"/>
+      <c r="K114" s="175"/>
       <c r="L114" s="13"/>
     </row>
     <row r="115" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13137,17 +13137,17 @@
       <c r="B115" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C115" s="186" t="s">
+      <c r="C115" s="174" t="s">
         <v>303</v>
       </c>
-      <c r="D115" s="177"/>
-      <c r="E115" s="177"/>
-      <c r="F115" s="177"/>
-      <c r="G115" s="177"/>
-      <c r="H115" s="177"/>
-      <c r="I115" s="177"/>
-      <c r="J115" s="177"/>
-      <c r="K115" s="177"/>
+      <c r="D115" s="175"/>
+      <c r="E115" s="175"/>
+      <c r="F115" s="175"/>
+      <c r="G115" s="175"/>
+      <c r="H115" s="175"/>
+      <c r="I115" s="175"/>
+      <c r="J115" s="175"/>
+      <c r="K115" s="175"/>
       <c r="L115" s="13"/>
     </row>
     <row r="116" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13155,15 +13155,15 @@
       <c r="B116" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C116" s="186"/>
-      <c r="D116" s="177"/>
-      <c r="E116" s="177"/>
-      <c r="F116" s="177"/>
-      <c r="G116" s="177"/>
-      <c r="H116" s="177"/>
-      <c r="I116" s="177"/>
-      <c r="J116" s="177"/>
-      <c r="K116" s="177"/>
+      <c r="C116" s="174"/>
+      <c r="D116" s="175"/>
+      <c r="E116" s="175"/>
+      <c r="F116" s="175"/>
+      <c r="G116" s="175"/>
+      <c r="H116" s="175"/>
+      <c r="I116" s="175"/>
+      <c r="J116" s="175"/>
+      <c r="K116" s="175"/>
       <c r="L116" s="13"/>
     </row>
     <row r="117" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -13185,17 +13185,17 @@
       <c r="B118" s="48" t="s">
         <v>304</v>
       </c>
-      <c r="C118" s="194" t="s">
+      <c r="C118" s="180" t="s">
         <v>305</v>
       </c>
-      <c r="D118" s="175"/>
-      <c r="E118" s="175"/>
-      <c r="F118" s="175"/>
-      <c r="G118" s="175"/>
-      <c r="H118" s="175"/>
-      <c r="I118" s="175"/>
-      <c r="J118" s="175"/>
-      <c r="K118" s="175"/>
+      <c r="D118" s="179"/>
+      <c r="E118" s="179"/>
+      <c r="F118" s="179"/>
+      <c r="G118" s="179"/>
+      <c r="H118" s="179"/>
+      <c r="I118" s="179"/>
+      <c r="J118" s="179"/>
+      <c r="K118" s="179"/>
       <c r="L118" s="58"/>
     </row>
     <row r="119" spans="1:12" ht="26.85" customHeight="1">
@@ -13203,17 +13203,17 @@
       <c r="B119" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="C119" s="192" t="s">
+      <c r="C119" s="176" t="s">
         <v>306</v>
       </c>
-      <c r="D119" s="188"/>
-      <c r="E119" s="188"/>
-      <c r="F119" s="188"/>
-      <c r="G119" s="188"/>
-      <c r="H119" s="188"/>
-      <c r="I119" s="188"/>
-      <c r="J119" s="188"/>
-      <c r="K119" s="188"/>
+      <c r="D119" s="177"/>
+      <c r="E119" s="177"/>
+      <c r="F119" s="177"/>
+      <c r="G119" s="177"/>
+      <c r="H119" s="177"/>
+      <c r="I119" s="177"/>
+      <c r="J119" s="177"/>
+      <c r="K119" s="177"/>
       <c r="L119" s="22"/>
     </row>
     <row r="120" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -15646,17 +15646,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C111:K111"/>
+    <mergeCell ref="C112:K112"/>
+    <mergeCell ref="C113:K113"/>
+    <mergeCell ref="C114:K114"/>
     <mergeCell ref="C116:K116"/>
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C119:K119"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="C118:K118"/>
     <mergeCell ref="C115:K115"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C111:K111"/>
-    <mergeCell ref="C112:K112"/>
-    <mergeCell ref="C113:K113"/>
-    <mergeCell ref="C114:K114"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -15681,20 +15681,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="181" t="s">
         <v>307</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -15770,17 +15770,17 @@
       <c r="B4" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="193" t="s">
+      <c r="C4" s="178" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="175"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="179"/>
+      <c r="I4" s="179"/>
+      <c r="J4" s="179"/>
+      <c r="K4" s="179"/>
       <c r="L4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="26.85" customHeight="1">
@@ -15788,17 +15788,17 @@
       <c r="B5" s="51" t="s">
         <v>308</v>
       </c>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="176" t="s">
         <v>309</v>
       </c>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="188"/>
-      <c r="K5" s="188"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
       <c r="L5" s="22"/>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -15993,18 +15993,18 @@
       <c r="B13" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="184" t="str">
+      <c r="C13" s="182" t="str">
         <f t="array" ref="C13">IF(C14="","?",C14)&amp;IF(C15="","","; downloaded "&amp;C15)&amp;IF(C16="","","; "&amp;C16)</f>
         <v>https://www.statistik.at/fileadmin/pages/410/Kap_H_Fertilitaet_2024.ods, https://www.statistik.at/statistiken/bevoelkerung-und-soziales/bevoelkerung/demographische-indikatoren-und-tafeln/demographische-querschnittsindikatoren, https://www.statistik.at/fileadmin/announcement/2025/02/20250226Geburtenbilanz2024.pdf; downloaded 2026-05-20</v>
       </c>
-      <c r="D13" s="177"/>
-      <c r="E13" s="177"/>
-      <c r="F13" s="177"/>
-      <c r="G13" s="177"/>
-      <c r="H13" s="177"/>
-      <c r="I13" s="177"/>
-      <c r="J13" s="177"/>
-      <c r="K13" s="177"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="175"/>
+      <c r="F13" s="175"/>
+      <c r="G13" s="175"/>
+      <c r="H13" s="175"/>
+      <c r="I13" s="175"/>
+      <c r="J13" s="175"/>
+      <c r="K13" s="175"/>
       <c r="L13" s="13"/>
     </row>
     <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16012,17 +16012,17 @@
       <c r="B14" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="185" t="s">
+      <c r="C14" s="183" t="s">
         <v>318</v>
       </c>
-      <c r="D14" s="177"/>
-      <c r="E14" s="177"/>
-      <c r="F14" s="177"/>
-      <c r="G14" s="177"/>
-      <c r="H14" s="177"/>
-      <c r="I14" s="177"/>
-      <c r="J14" s="177"/>
-      <c r="K14" s="177"/>
+      <c r="D14" s="175"/>
+      <c r="E14" s="175"/>
+      <c r="F14" s="175"/>
+      <c r="G14" s="175"/>
+      <c r="H14" s="175"/>
+      <c r="I14" s="175"/>
+      <c r="J14" s="175"/>
+      <c r="K14" s="175"/>
       <c r="L14" s="13"/>
     </row>
     <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16030,17 +16030,17 @@
       <c r="B15" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="185" t="s">
+      <c r="C15" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="177"/>
-      <c r="E15" s="177"/>
-      <c r="F15" s="177"/>
-      <c r="G15" s="177"/>
-      <c r="H15" s="177"/>
-      <c r="I15" s="177"/>
-      <c r="J15" s="177"/>
-      <c r="K15" s="177"/>
+      <c r="D15" s="175"/>
+      <c r="E15" s="175"/>
+      <c r="F15" s="175"/>
+      <c r="G15" s="175"/>
+      <c r="H15" s="175"/>
+      <c r="I15" s="175"/>
+      <c r="J15" s="175"/>
+      <c r="K15" s="175"/>
       <c r="L15" s="13"/>
     </row>
     <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16048,15 +16048,15 @@
       <c r="B16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="186"/>
-      <c r="D16" s="177"/>
-      <c r="E16" s="177"/>
-      <c r="F16" s="177"/>
-      <c r="G16" s="177"/>
-      <c r="H16" s="177"/>
-      <c r="I16" s="177"/>
-      <c r="J16" s="177"/>
-      <c r="K16" s="177"/>
+      <c r="C16" s="174"/>
+      <c r="D16" s="175"/>
+      <c r="E16" s="175"/>
+      <c r="F16" s="175"/>
+      <c r="G16" s="175"/>
+      <c r="H16" s="175"/>
+      <c r="I16" s="175"/>
+      <c r="J16" s="175"/>
+      <c r="K16" s="175"/>
       <c r="L16" s="13"/>
     </row>
     <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16064,17 +16064,17 @@
       <c r="B17" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="186" t="s">
+      <c r="C17" s="174" t="s">
         <v>319</v>
       </c>
-      <c r="D17" s="177"/>
-      <c r="E17" s="177"/>
-      <c r="F17" s="177"/>
-      <c r="G17" s="177"/>
-      <c r="H17" s="177"/>
-      <c r="I17" s="177"/>
-      <c r="J17" s="177"/>
-      <c r="K17" s="177"/>
+      <c r="D17" s="175"/>
+      <c r="E17" s="175"/>
+      <c r="F17" s="175"/>
+      <c r="G17" s="175"/>
+      <c r="H17" s="175"/>
+      <c r="I17" s="175"/>
+      <c r="J17" s="175"/>
+      <c r="K17" s="175"/>
       <c r="L17" s="13"/>
     </row>
     <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16082,15 +16082,15 @@
       <c r="B18" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="186"/>
-      <c r="D18" s="177"/>
-      <c r="E18" s="177"/>
-      <c r="F18" s="177"/>
-      <c r="G18" s="177"/>
-      <c r="H18" s="177"/>
-      <c r="I18" s="177"/>
-      <c r="J18" s="177"/>
-      <c r="K18" s="177"/>
+      <c r="C18" s="174"/>
+      <c r="D18" s="175"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="175"/>
+      <c r="G18" s="175"/>
+      <c r="H18" s="175"/>
+      <c r="I18" s="175"/>
+      <c r="J18" s="175"/>
+      <c r="K18" s="175"/>
       <c r="L18" s="13"/>
     </row>
     <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -16115,14 +16115,14 @@
       <c r="C20" s="195" t="s">
         <v>321</v>
       </c>
-      <c r="D20" s="177"/>
-      <c r="E20" s="177"/>
-      <c r="F20" s="177"/>
-      <c r="G20" s="177"/>
-      <c r="H20" s="177"/>
-      <c r="I20" s="177"/>
-      <c r="J20" s="177"/>
-      <c r="K20" s="177"/>
+      <c r="D20" s="175"/>
+      <c r="E20" s="175"/>
+      <c r="F20" s="175"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="175"/>
+      <c r="I20" s="175"/>
+      <c r="J20" s="175"/>
+      <c r="K20" s="175"/>
       <c r="L20" s="22"/>
     </row>
     <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17780,18 +17780,18 @@
       <c r="B59" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="184" t="str">
+      <c r="C59" s="182" t="str">
         <f t="array" ref="C59">IF(C60="","?",C60)&amp;IF(C61="","","; downloaded "&amp;C61)&amp;IF(C62="","","; "&amp;C62)</f>
         <v>Quelle wie Fertility-Sektion oben, siehe C14. https://www.statistik.at/fileadmin/pages/410/Kap_H_Fertilitaet_2024.ods, https://www.statistik.at/statistiken/bevoelkerung-und-soziales/bevoelkerung/demographische-indikatoren-und-tafeln/demographische-querschnittsindikatoren, https://www.statistik.at/fileadmin/announcement/2025/02/20250226Geburtenbilanz2024.pdf; downloaded 2026-05-20</v>
       </c>
-      <c r="D59" s="177"/>
-      <c r="E59" s="177"/>
-      <c r="F59" s="177"/>
-      <c r="G59" s="177"/>
-      <c r="H59" s="177"/>
-      <c r="I59" s="177"/>
-      <c r="J59" s="177"/>
-      <c r="K59" s="177"/>
+      <c r="D59" s="175"/>
+      <c r="E59" s="175"/>
+      <c r="F59" s="175"/>
+      <c r="G59" s="175"/>
+      <c r="H59" s="175"/>
+      <c r="I59" s="175"/>
+      <c r="J59" s="175"/>
+      <c r="K59" s="175"/>
       <c r="L59" s="13"/>
     </row>
     <row r="60" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17799,17 +17799,17 @@
       <c r="B60" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C60" s="185" t="s">
+      <c r="C60" s="183" t="s">
         <v>394</v>
       </c>
-      <c r="D60" s="177"/>
-      <c r="E60" s="177"/>
-      <c r="F60" s="177"/>
-      <c r="G60" s="177"/>
-      <c r="H60" s="177"/>
-      <c r="I60" s="177"/>
-      <c r="J60" s="177"/>
-      <c r="K60" s="177"/>
+      <c r="D60" s="175"/>
+      <c r="E60" s="175"/>
+      <c r="F60" s="175"/>
+      <c r="G60" s="175"/>
+      <c r="H60" s="175"/>
+      <c r="I60" s="175"/>
+      <c r="J60" s="175"/>
+      <c r="K60" s="175"/>
       <c r="L60" s="13"/>
     </row>
     <row r="61" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17817,17 +17817,17 @@
       <c r="B61" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C61" s="185" t="s">
+      <c r="C61" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="D61" s="177"/>
-      <c r="E61" s="177"/>
-      <c r="F61" s="177"/>
-      <c r="G61" s="177"/>
-      <c r="H61" s="177"/>
-      <c r="I61" s="177"/>
-      <c r="J61" s="177"/>
-      <c r="K61" s="177"/>
+      <c r="D61" s="175"/>
+      <c r="E61" s="175"/>
+      <c r="F61" s="175"/>
+      <c r="G61" s="175"/>
+      <c r="H61" s="175"/>
+      <c r="I61" s="175"/>
+      <c r="J61" s="175"/>
+      <c r="K61" s="175"/>
       <c r="L61" s="13"/>
     </row>
     <row r="62" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17835,15 +17835,15 @@
       <c r="B62" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C62" s="186"/>
-      <c r="D62" s="177"/>
-      <c r="E62" s="177"/>
-      <c r="F62" s="177"/>
-      <c r="G62" s="177"/>
-      <c r="H62" s="177"/>
-      <c r="I62" s="177"/>
-      <c r="J62" s="177"/>
-      <c r="K62" s="177"/>
+      <c r="C62" s="174"/>
+      <c r="D62" s="175"/>
+      <c r="E62" s="175"/>
+      <c r="F62" s="175"/>
+      <c r="G62" s="175"/>
+      <c r="H62" s="175"/>
+      <c r="I62" s="175"/>
+      <c r="J62" s="175"/>
+      <c r="K62" s="175"/>
       <c r="L62" s="13"/>
     </row>
     <row r="63" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17851,17 +17851,17 @@
       <c r="B63" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C63" s="186" t="s">
+      <c r="C63" s="174" t="s">
         <v>395</v>
       </c>
-      <c r="D63" s="177"/>
-      <c r="E63" s="177"/>
-      <c r="F63" s="177"/>
-      <c r="G63" s="177"/>
-      <c r="H63" s="177"/>
-      <c r="I63" s="177"/>
-      <c r="J63" s="177"/>
-      <c r="K63" s="177"/>
+      <c r="D63" s="175"/>
+      <c r="E63" s="175"/>
+      <c r="F63" s="175"/>
+      <c r="G63" s="175"/>
+      <c r="H63" s="175"/>
+      <c r="I63" s="175"/>
+      <c r="J63" s="175"/>
+      <c r="K63" s="175"/>
       <c r="L63" s="13"/>
     </row>
     <row r="64" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17869,15 +17869,15 @@
       <c r="B64" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C64" s="186"/>
-      <c r="D64" s="177"/>
-      <c r="E64" s="177"/>
-      <c r="F64" s="177"/>
-      <c r="G64" s="177"/>
-      <c r="H64" s="177"/>
-      <c r="I64" s="177"/>
-      <c r="J64" s="177"/>
-      <c r="K64" s="177"/>
+      <c r="C64" s="174"/>
+      <c r="D64" s="175"/>
+      <c r="E64" s="175"/>
+      <c r="F64" s="175"/>
+      <c r="G64" s="175"/>
+      <c r="H64" s="175"/>
+      <c r="I64" s="175"/>
+      <c r="J64" s="175"/>
+      <c r="K64" s="175"/>
       <c r="L64" s="13"/>
     </row>
     <row r="65" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -17899,17 +17899,17 @@
       <c r="B66" s="48" t="s">
         <v>304</v>
       </c>
-      <c r="C66" s="194" t="s">
+      <c r="C66" s="180" t="s">
         <v>305</v>
       </c>
-      <c r="D66" s="175"/>
-      <c r="E66" s="175"/>
-      <c r="F66" s="175"/>
-      <c r="G66" s="175"/>
-      <c r="H66" s="175"/>
-      <c r="I66" s="175"/>
-      <c r="J66" s="175"/>
-      <c r="K66" s="175"/>
+      <c r="D66" s="179"/>
+      <c r="E66" s="179"/>
+      <c r="F66" s="179"/>
+      <c r="G66" s="179"/>
+      <c r="H66" s="179"/>
+      <c r="I66" s="179"/>
+      <c r="J66" s="179"/>
+      <c r="K66" s="179"/>
       <c r="L66" s="58"/>
     </row>
     <row r="67" spans="1:12" ht="26.85" customHeight="1">
@@ -17917,17 +17917,17 @@
       <c r="B67" s="51" t="s">
         <v>320</v>
       </c>
-      <c r="C67" s="192" t="s">
+      <c r="C67" s="176" t="s">
         <v>396</v>
       </c>
-      <c r="D67" s="188"/>
-      <c r="E67" s="188"/>
-      <c r="F67" s="188"/>
-      <c r="G67" s="188"/>
-      <c r="H67" s="188"/>
-      <c r="I67" s="188"/>
-      <c r="J67" s="188"/>
-      <c r="K67" s="188"/>
+      <c r="D67" s="177"/>
+      <c r="E67" s="177"/>
+      <c r="F67" s="177"/>
+      <c r="G67" s="177"/>
+      <c r="H67" s="177"/>
+      <c r="I67" s="177"/>
+      <c r="J67" s="177"/>
+      <c r="K67" s="177"/>
       <c r="L67" s="22"/>
     </row>
     <row r="68" spans="1:12" ht="32.1" customHeight="1">
@@ -18834,6 +18834,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C59:K59"/>
+    <mergeCell ref="C60:K60"/>
+    <mergeCell ref="C61:K61"/>
+    <mergeCell ref="C62:K62"/>
+    <mergeCell ref="C4:K4"/>
     <mergeCell ref="C64:K64"/>
     <mergeCell ref="C20:K20"/>
     <mergeCell ref="C67:K67"/>
@@ -18846,12 +18852,6 @@
     <mergeCell ref="C66:K66"/>
     <mergeCell ref="C63:K63"/>
     <mergeCell ref="C17:K17"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C59:K59"/>
-    <mergeCell ref="C60:K60"/>
-    <mergeCell ref="C61:K61"/>
-    <mergeCell ref="C62:K62"/>
-    <mergeCell ref="C4:K4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -18876,20 +18876,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="181" t="s">
         <v>402</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -18986,14 +18986,14 @@
       <c r="C5" s="195" t="s">
         <v>404</v>
       </c>
-      <c r="D5" s="177"/>
-      <c r="E5" s="177"/>
-      <c r="F5" s="177"/>
-      <c r="G5" s="177"/>
-      <c r="H5" s="177"/>
-      <c r="I5" s="177"/>
-      <c r="J5" s="177"/>
-      <c r="K5" s="177"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="175"/>
+      <c r="G5" s="175"/>
+      <c r="H5" s="175"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="175"/>
       <c r="L5" s="22"/>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23576,18 +23576,18 @@
       <c r="B109" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C109" s="184" t="str">
+      <c r="C109" s="182" t="str">
         <f t="array" ref="C109">IF(C110="","?",C110)&amp;IF(C111="","","; downloaded "&amp;C111)&amp;IF(C112="","","; "&amp;C112)</f>
         <v>https://www.statistik.at/statistiken/bevoelkerung-und-soziales/bevoelkerung/gestorbene/demographische-merkmale-von-gestorbenen, https://www.statistik.at/fileadmin/pages/428/neu_Gestorbene__nach__demographischen__Merkmalen.ods; downloaded 2026-05-20</v>
       </c>
-      <c r="D109" s="177"/>
-      <c r="E109" s="177"/>
-      <c r="F109" s="177"/>
-      <c r="G109" s="177"/>
-      <c r="H109" s="177"/>
-      <c r="I109" s="177"/>
-      <c r="J109" s="177"/>
-      <c r="K109" s="177"/>
+      <c r="D109" s="175"/>
+      <c r="E109" s="175"/>
+      <c r="F109" s="175"/>
+      <c r="G109" s="175"/>
+      <c r="H109" s="175"/>
+      <c r="I109" s="175"/>
+      <c r="J109" s="175"/>
+      <c r="K109" s="175"/>
       <c r="L109" s="13"/>
     </row>
     <row r="110" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23595,17 +23595,17 @@
       <c r="B110" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C110" s="185" t="s">
+      <c r="C110" s="183" t="s">
         <v>607</v>
       </c>
-      <c r="D110" s="177"/>
-      <c r="E110" s="177"/>
-      <c r="F110" s="177"/>
-      <c r="G110" s="177"/>
-      <c r="H110" s="177"/>
-      <c r="I110" s="177"/>
-      <c r="J110" s="177"/>
-      <c r="K110" s="177"/>
+      <c r="D110" s="175"/>
+      <c r="E110" s="175"/>
+      <c r="F110" s="175"/>
+      <c r="G110" s="175"/>
+      <c r="H110" s="175"/>
+      <c r="I110" s="175"/>
+      <c r="J110" s="175"/>
+      <c r="K110" s="175"/>
       <c r="L110" s="13"/>
     </row>
     <row r="111" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23613,17 +23613,17 @@
       <c r="B111" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C111" s="185" t="s">
+      <c r="C111" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="D111" s="177"/>
-      <c r="E111" s="177"/>
-      <c r="F111" s="177"/>
-      <c r="G111" s="177"/>
-      <c r="H111" s="177"/>
-      <c r="I111" s="177"/>
-      <c r="J111" s="177"/>
-      <c r="K111" s="177"/>
+      <c r="D111" s="175"/>
+      <c r="E111" s="175"/>
+      <c r="F111" s="175"/>
+      <c r="G111" s="175"/>
+      <c r="H111" s="175"/>
+      <c r="I111" s="175"/>
+      <c r="J111" s="175"/>
+      <c r="K111" s="175"/>
       <c r="L111" s="13"/>
     </row>
     <row r="112" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23631,15 +23631,15 @@
       <c r="B112" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C112" s="186"/>
-      <c r="D112" s="177"/>
-      <c r="E112" s="177"/>
-      <c r="F112" s="177"/>
-      <c r="G112" s="177"/>
-      <c r="H112" s="177"/>
-      <c r="I112" s="177"/>
-      <c r="J112" s="177"/>
-      <c r="K112" s="177"/>
+      <c r="C112" s="174"/>
+      <c r="D112" s="175"/>
+      <c r="E112" s="175"/>
+      <c r="F112" s="175"/>
+      <c r="G112" s="175"/>
+      <c r="H112" s="175"/>
+      <c r="I112" s="175"/>
+      <c r="J112" s="175"/>
+      <c r="K112" s="175"/>
       <c r="L112" s="13"/>
     </row>
     <row r="113" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23647,17 +23647,17 @@
       <c r="B113" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C113" s="186" t="s">
+      <c r="C113" s="174" t="s">
         <v>608</v>
       </c>
-      <c r="D113" s="177"/>
-      <c r="E113" s="177"/>
-      <c r="F113" s="177"/>
-      <c r="G113" s="177"/>
-      <c r="H113" s="177"/>
-      <c r="I113" s="177"/>
-      <c r="J113" s="177"/>
-      <c r="K113" s="177"/>
+      <c r="D113" s="175"/>
+      <c r="E113" s="175"/>
+      <c r="F113" s="175"/>
+      <c r="G113" s="175"/>
+      <c r="H113" s="175"/>
+      <c r="I113" s="175"/>
+      <c r="J113" s="175"/>
+      <c r="K113" s="175"/>
       <c r="L113" s="13"/>
     </row>
     <row r="114" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23665,15 +23665,15 @@
       <c r="B114" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C114" s="186"/>
-      <c r="D114" s="177"/>
-      <c r="E114" s="177"/>
-      <c r="F114" s="177"/>
-      <c r="G114" s="177"/>
-      <c r="H114" s="177"/>
-      <c r="I114" s="177"/>
-      <c r="J114" s="177"/>
-      <c r="K114" s="177"/>
+      <c r="C114" s="174"/>
+      <c r="D114" s="175"/>
+      <c r="E114" s="175"/>
+      <c r="F114" s="175"/>
+      <c r="G114" s="175"/>
+      <c r="H114" s="175"/>
+      <c r="I114" s="175"/>
+      <c r="J114" s="175"/>
+      <c r="K114" s="175"/>
       <c r="L114" s="13"/>
     </row>
     <row r="115" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -23698,14 +23698,14 @@
       <c r="C116" s="198" t="s">
         <v>305</v>
       </c>
-      <c r="D116" s="177"/>
-      <c r="E116" s="177"/>
-      <c r="F116" s="177"/>
-      <c r="G116" s="177"/>
-      <c r="H116" s="177"/>
-      <c r="I116" s="177"/>
-      <c r="J116" s="177"/>
-      <c r="K116" s="177"/>
+      <c r="D116" s="175"/>
+      <c r="E116" s="175"/>
+      <c r="F116" s="175"/>
+      <c r="G116" s="175"/>
+      <c r="H116" s="175"/>
+      <c r="I116" s="175"/>
+      <c r="J116" s="175"/>
+      <c r="K116" s="175"/>
       <c r="L116" s="58"/>
     </row>
     <row r="117" spans="1:12" ht="26.85" customHeight="1">
@@ -23716,13 +23716,13 @@
       <c r="C117" s="196" t="s">
         <v>609</v>
       </c>
-      <c r="D117" s="177"/>
-      <c r="E117" s="177"/>
-      <c r="F117" s="177"/>
-      <c r="G117" s="177"/>
-      <c r="H117" s="177"/>
-      <c r="I117" s="177"/>
-      <c r="J117" s="177"/>
+      <c r="D117" s="175"/>
+      <c r="E117" s="175"/>
+      <c r="F117" s="175"/>
+      <c r="G117" s="175"/>
+      <c r="H117" s="175"/>
+      <c r="I117" s="175"/>
+      <c r="J117" s="175"/>
       <c r="K117" s="197"/>
       <c r="L117" s="104"/>
     </row>
@@ -26156,17 +26156,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C109:K109"/>
+    <mergeCell ref="C110:K110"/>
+    <mergeCell ref="C111:K111"/>
+    <mergeCell ref="C112:K112"/>
     <mergeCell ref="C114:K114"/>
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C117:K117"/>
     <mergeCell ref="C116:K116"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="C113:K113"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C109:K109"/>
-    <mergeCell ref="C110:K110"/>
-    <mergeCell ref="C111:K111"/>
-    <mergeCell ref="C112:K112"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -26191,20 +26191,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="181" t="s">
         <v>610</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -26280,17 +26280,17 @@
       <c r="B4" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="193" t="s">
+      <c r="C4" s="178" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="175"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="179"/>
+      <c r="I4" s="179"/>
+      <c r="J4" s="179"/>
+      <c r="K4" s="179"/>
       <c r="L4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="26.85" customHeight="1">
@@ -26298,17 +26298,17 @@
       <c r="B5" s="51" t="s">
         <v>611</v>
       </c>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="176" t="s">
         <v>612</v>
       </c>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="188"/>
-      <c r="K5" s="188"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
       <c r="L5" s="22"/>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -31082,18 +31082,18 @@
       <c r="B113" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C113" s="184" t="str">
+      <c r="C113" s="182" t="str">
         <f t="array" ref="C113">IF(C114="","?",C114)&amp;IF(C115="","","; downloaded "&amp;C115)&amp;IF(C116="","","; "&amp;C116)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/migr_imm3ctb, https://ec.europa.eu/eurostat/databrowser/view/migr_emi4ctb, https://www.statistik.at/fileadmin/pages/432/Tabellensammlung_Aussenwanderungen_2024.ods; downloaded 2026-05-20; we used the 10-year average number of the migration balance (2015-2024); the numbers are binomially distributed between the age of 5 and 54</v>
       </c>
-      <c r="D113" s="177"/>
-      <c r="E113" s="177"/>
-      <c r="F113" s="177"/>
-      <c r="G113" s="177"/>
-      <c r="H113" s="177"/>
-      <c r="I113" s="177"/>
-      <c r="J113" s="177"/>
-      <c r="K113" s="177"/>
+      <c r="D113" s="175"/>
+      <c r="E113" s="175"/>
+      <c r="F113" s="175"/>
+      <c r="G113" s="175"/>
+      <c r="H113" s="175"/>
+      <c r="I113" s="175"/>
+      <c r="J113" s="175"/>
+      <c r="K113" s="175"/>
       <c r="L113" s="13"/>
     </row>
     <row r="114" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -31101,17 +31101,17 @@
       <c r="B114" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C114" s="185" t="s">
+      <c r="C114" s="183" t="s">
         <v>717</v>
       </c>
-      <c r="D114" s="177"/>
-      <c r="E114" s="177"/>
-      <c r="F114" s="177"/>
-      <c r="G114" s="177"/>
-      <c r="H114" s="177"/>
-      <c r="I114" s="177"/>
-      <c r="J114" s="177"/>
-      <c r="K114" s="177"/>
+      <c r="D114" s="175"/>
+      <c r="E114" s="175"/>
+      <c r="F114" s="175"/>
+      <c r="G114" s="175"/>
+      <c r="H114" s="175"/>
+      <c r="I114" s="175"/>
+      <c r="J114" s="175"/>
+      <c r="K114" s="175"/>
       <c r="L114" s="13"/>
     </row>
     <row r="115" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -31122,14 +31122,14 @@
       <c r="C115" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="D115" s="182"/>
-      <c r="E115" s="182"/>
-      <c r="F115" s="182"/>
-      <c r="G115" s="182"/>
-      <c r="H115" s="182"/>
-      <c r="I115" s="182"/>
-      <c r="J115" s="182"/>
-      <c r="K115" s="182"/>
+      <c r="D115" s="187"/>
+      <c r="E115" s="187"/>
+      <c r="F115" s="187"/>
+      <c r="G115" s="187"/>
+      <c r="H115" s="187"/>
+      <c r="I115" s="187"/>
+      <c r="J115" s="187"/>
+      <c r="K115" s="187"/>
       <c r="L115" s="13"/>
     </row>
     <row r="116" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -31137,17 +31137,17 @@
       <c r="B116" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C116" s="202" t="s">
+      <c r="C116" s="204" t="s">
         <v>718</v>
       </c>
-      <c r="D116" s="175"/>
-      <c r="E116" s="175"/>
-      <c r="F116" s="175"/>
-      <c r="G116" s="175"/>
-      <c r="H116" s="175"/>
-      <c r="I116" s="175"/>
-      <c r="J116" s="175"/>
-      <c r="K116" s="175"/>
+      <c r="D116" s="179"/>
+      <c r="E116" s="179"/>
+      <c r="F116" s="179"/>
+      <c r="G116" s="179"/>
+      <c r="H116" s="179"/>
+      <c r="I116" s="179"/>
+      <c r="J116" s="179"/>
+      <c r="K116" s="179"/>
       <c r="L116" s="13"/>
     </row>
     <row r="117" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -31155,17 +31155,17 @@
       <c r="B117" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C117" s="203" t="s">
+      <c r="C117" s="202" t="s">
         <v>719</v>
       </c>
-      <c r="D117" s="188"/>
-      <c r="E117" s="188"/>
-      <c r="F117" s="188"/>
-      <c r="G117" s="188"/>
-      <c r="H117" s="188"/>
-      <c r="I117" s="188"/>
-      <c r="J117" s="188"/>
-      <c r="K117" s="188"/>
+      <c r="D117" s="177"/>
+      <c r="E117" s="177"/>
+      <c r="F117" s="177"/>
+      <c r="G117" s="177"/>
+      <c r="H117" s="177"/>
+      <c r="I117" s="177"/>
+      <c r="J117" s="177"/>
+      <c r="K117" s="177"/>
       <c r="L117" s="13"/>
     </row>
     <row r="118" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -31173,15 +31173,15 @@
       <c r="B118" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C118" s="186"/>
-      <c r="D118" s="177"/>
-      <c r="E118" s="177"/>
-      <c r="F118" s="177"/>
-      <c r="G118" s="177"/>
-      <c r="H118" s="177"/>
-      <c r="I118" s="177"/>
-      <c r="J118" s="177"/>
-      <c r="K118" s="177"/>
+      <c r="C118" s="174"/>
+      <c r="D118" s="175"/>
+      <c r="E118" s="175"/>
+      <c r="F118" s="175"/>
+      <c r="G118" s="175"/>
+      <c r="H118" s="175"/>
+      <c r="I118" s="175"/>
+      <c r="J118" s="175"/>
+      <c r="K118" s="175"/>
       <c r="L118" s="13"/>
     </row>
     <row r="119" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -31206,14 +31206,14 @@
       <c r="C120" s="198" t="s">
         <v>305</v>
       </c>
-      <c r="D120" s="177"/>
-      <c r="E120" s="177"/>
-      <c r="F120" s="177"/>
-      <c r="G120" s="177"/>
-      <c r="H120" s="177"/>
-      <c r="I120" s="177"/>
-      <c r="J120" s="177"/>
-      <c r="K120" s="177"/>
+      <c r="D120" s="175"/>
+      <c r="E120" s="175"/>
+      <c r="F120" s="175"/>
+      <c r="G120" s="175"/>
+      <c r="H120" s="175"/>
+      <c r="I120" s="175"/>
+      <c r="J120" s="175"/>
+      <c r="K120" s="175"/>
       <c r="L120" s="58"/>
     </row>
     <row r="121" spans="1:12" ht="32.1" customHeight="1">
@@ -31224,14 +31224,14 @@
       <c r="C121" s="195" t="s">
         <v>721</v>
       </c>
-      <c r="D121" s="177"/>
-      <c r="E121" s="177"/>
-      <c r="F121" s="177"/>
-      <c r="G121" s="177"/>
-      <c r="H121" s="177"/>
-      <c r="I121" s="177"/>
-      <c r="J121" s="177"/>
-      <c r="K121" s="177"/>
+      <c r="D121" s="175"/>
+      <c r="E121" s="175"/>
+      <c r="F121" s="175"/>
+      <c r="G121" s="175"/>
+      <c r="H121" s="175"/>
+      <c r="I121" s="175"/>
+      <c r="J121" s="175"/>
+      <c r="K121" s="175"/>
       <c r="L121" s="22"/>
     </row>
     <row r="122" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -33946,18 +33946,18 @@
       <c r="B201" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C201" s="184" t="str">
+      <c r="C201" s="182" t="str">
         <f t="array" ref="C201">IF(C202="","?",C202)&amp;IF(C203="","","; downloaded "&amp;C203)&amp;IF(C204="","","; "&amp;C204)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/migr_imm3ctb, https://ec.europa.eu/eurostat/databrowser/view/migr_emi4ctb, https://www.statistik.at/fileadmin/pages/432/Tabellensammlung_Aussenwanderungen_2024.ods; downloaded 2026-05-20</v>
       </c>
-      <c r="D201" s="177"/>
-      <c r="E201" s="177"/>
-      <c r="F201" s="177"/>
-      <c r="G201" s="177"/>
-      <c r="H201" s="177"/>
-      <c r="I201" s="177"/>
-      <c r="J201" s="177"/>
-      <c r="K201" s="177"/>
+      <c r="D201" s="175"/>
+      <c r="E201" s="175"/>
+      <c r="F201" s="175"/>
+      <c r="G201" s="175"/>
+      <c r="H201" s="175"/>
+      <c r="I201" s="175"/>
+      <c r="J201" s="175"/>
+      <c r="K201" s="175"/>
       <c r="L201" s="13"/>
     </row>
     <row r="202" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -33965,17 +33965,17 @@
       <c r="B202" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C202" s="185" t="s">
+      <c r="C202" s="183" t="s">
         <v>717</v>
       </c>
-      <c r="D202" s="177"/>
-      <c r="E202" s="177"/>
-      <c r="F202" s="177"/>
-      <c r="G202" s="177"/>
-      <c r="H202" s="177"/>
-      <c r="I202" s="177"/>
-      <c r="J202" s="177"/>
-      <c r="K202" s="177"/>
+      <c r="D202" s="175"/>
+      <c r="E202" s="175"/>
+      <c r="F202" s="175"/>
+      <c r="G202" s="175"/>
+      <c r="H202" s="175"/>
+      <c r="I202" s="175"/>
+      <c r="J202" s="175"/>
+      <c r="K202" s="175"/>
       <c r="L202" s="13"/>
     </row>
     <row r="203" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -33983,17 +33983,17 @@
       <c r="B203" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C203" s="185" t="s">
+      <c r="C203" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="D203" s="177"/>
-      <c r="E203" s="177"/>
-      <c r="F203" s="177"/>
-      <c r="G203" s="177"/>
-      <c r="H203" s="177"/>
-      <c r="I203" s="177"/>
-      <c r="J203" s="177"/>
-      <c r="K203" s="177"/>
+      <c r="D203" s="175"/>
+      <c r="E203" s="175"/>
+      <c r="F203" s="175"/>
+      <c r="G203" s="175"/>
+      <c r="H203" s="175"/>
+      <c r="I203" s="175"/>
+      <c r="J203" s="175"/>
+      <c r="K203" s="175"/>
       <c r="L203" s="13"/>
     </row>
     <row r="204" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -34002,14 +34002,14 @@
         <v>81</v>
       </c>
       <c r="C204" s="201"/>
-      <c r="D204" s="182"/>
-      <c r="E204" s="182"/>
-      <c r="F204" s="182"/>
-      <c r="G204" s="182"/>
-      <c r="H204" s="182"/>
-      <c r="I204" s="182"/>
-      <c r="J204" s="182"/>
-      <c r="K204" s="182"/>
+      <c r="D204" s="187"/>
+      <c r="E204" s="187"/>
+      <c r="F204" s="187"/>
+      <c r="G204" s="187"/>
+      <c r="H204" s="187"/>
+      <c r="I204" s="187"/>
+      <c r="J204" s="187"/>
+      <c r="K204" s="187"/>
       <c r="L204" s="13"/>
     </row>
     <row r="205" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -34017,17 +34017,17 @@
       <c r="B205" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C205" s="204" t="s">
+      <c r="C205" s="203" t="s">
         <v>723</v>
       </c>
-      <c r="D205" s="175"/>
-      <c r="E205" s="175"/>
-      <c r="F205" s="175"/>
-      <c r="G205" s="175"/>
-      <c r="H205" s="175"/>
-      <c r="I205" s="175"/>
-      <c r="J205" s="175"/>
-      <c r="K205" s="175"/>
+      <c r="D205" s="179"/>
+      <c r="E205" s="179"/>
+      <c r="F205" s="179"/>
+      <c r="G205" s="179"/>
+      <c r="H205" s="179"/>
+      <c r="I205" s="179"/>
+      <c r="J205" s="179"/>
+      <c r="K205" s="179"/>
       <c r="L205" s="13"/>
     </row>
     <row r="206" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -34035,15 +34035,15 @@
       <c r="B206" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C206" s="203"/>
-      <c r="D206" s="188"/>
-      <c r="E206" s="188"/>
-      <c r="F206" s="188"/>
-      <c r="G206" s="188"/>
-      <c r="H206" s="188"/>
-      <c r="I206" s="188"/>
-      <c r="J206" s="188"/>
-      <c r="K206" s="188"/>
+      <c r="C206" s="202"/>
+      <c r="D206" s="177"/>
+      <c r="E206" s="177"/>
+      <c r="F206" s="177"/>
+      <c r="G206" s="177"/>
+      <c r="H206" s="177"/>
+      <c r="I206" s="177"/>
+      <c r="J206" s="177"/>
+      <c r="K206" s="177"/>
       <c r="L206" s="13"/>
     </row>
     <row r="207" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -34068,14 +34068,14 @@
       <c r="C208" s="195" t="s">
         <v>725</v>
       </c>
-      <c r="D208" s="177"/>
-      <c r="E208" s="177"/>
-      <c r="F208" s="177"/>
-      <c r="G208" s="177"/>
-      <c r="H208" s="177"/>
-      <c r="I208" s="177"/>
-      <c r="J208" s="177"/>
-      <c r="K208" s="177"/>
+      <c r="D208" s="175"/>
+      <c r="E208" s="175"/>
+      <c r="F208" s="175"/>
+      <c r="G208" s="175"/>
+      <c r="H208" s="175"/>
+      <c r="I208" s="175"/>
+      <c r="J208" s="175"/>
+      <c r="K208" s="175"/>
       <c r="L208" s="22"/>
     </row>
     <row r="209" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36860,18 +36860,18 @@
       <c r="B288" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C288" s="184" t="str">
+      <c r="C288" s="182" t="str">
         <f t="array" ref="C288">IF(C289="","?",C289)&amp;IF(C290="","","; downloaded "&amp;C290)&amp;IF(C291="","","; "&amp;C291)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/migr_imm3ctb, https://ec.europa.eu/eurostat/databrowser/view/migr_emi4ctb, https://www.statistik.at/fileadmin/pages/432/Tabellensammlung_Aussenwanderungen_2024.ods; downloaded 2026-05-20</v>
       </c>
-      <c r="D288" s="177"/>
-      <c r="E288" s="177"/>
-      <c r="F288" s="177"/>
-      <c r="G288" s="177"/>
-      <c r="H288" s="177"/>
-      <c r="I288" s="177"/>
-      <c r="J288" s="177"/>
-      <c r="K288" s="177"/>
+      <c r="D288" s="175"/>
+      <c r="E288" s="175"/>
+      <c r="F288" s="175"/>
+      <c r="G288" s="175"/>
+      <c r="H288" s="175"/>
+      <c r="I288" s="175"/>
+      <c r="J288" s="175"/>
+      <c r="K288" s="175"/>
       <c r="L288" s="13"/>
     </row>
     <row r="289" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36879,17 +36879,17 @@
       <c r="B289" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C289" s="185" t="s">
+      <c r="C289" s="183" t="s">
         <v>717</v>
       </c>
-      <c r="D289" s="177"/>
-      <c r="E289" s="177"/>
-      <c r="F289" s="177"/>
-      <c r="G289" s="177"/>
-      <c r="H289" s="177"/>
-      <c r="I289" s="177"/>
-      <c r="J289" s="177"/>
-      <c r="K289" s="177"/>
+      <c r="D289" s="175"/>
+      <c r="E289" s="175"/>
+      <c r="F289" s="175"/>
+      <c r="G289" s="175"/>
+      <c r="H289" s="175"/>
+      <c r="I289" s="175"/>
+      <c r="J289" s="175"/>
+      <c r="K289" s="175"/>
       <c r="L289" s="13"/>
     </row>
     <row r="290" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36897,17 +36897,17 @@
       <c r="B290" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C290" s="185" t="s">
+      <c r="C290" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="D290" s="177"/>
-      <c r="E290" s="177"/>
-      <c r="F290" s="177"/>
-      <c r="G290" s="177"/>
-      <c r="H290" s="177"/>
-      <c r="I290" s="177"/>
-      <c r="J290" s="177"/>
-      <c r="K290" s="177"/>
+      <c r="D290" s="175"/>
+      <c r="E290" s="175"/>
+      <c r="F290" s="175"/>
+      <c r="G290" s="175"/>
+      <c r="H290" s="175"/>
+      <c r="I290" s="175"/>
+      <c r="J290" s="175"/>
+      <c r="K290" s="175"/>
       <c r="L290" s="13"/>
     </row>
     <row r="291" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36916,14 +36916,14 @@
         <v>81</v>
       </c>
       <c r="C291" s="201"/>
-      <c r="D291" s="182"/>
-      <c r="E291" s="182"/>
-      <c r="F291" s="182"/>
-      <c r="G291" s="182"/>
-      <c r="H291" s="182"/>
-      <c r="I291" s="182"/>
-      <c r="J291" s="182"/>
-      <c r="K291" s="182"/>
+      <c r="D291" s="187"/>
+      <c r="E291" s="187"/>
+      <c r="F291" s="187"/>
+      <c r="G291" s="187"/>
+      <c r="H291" s="187"/>
+      <c r="I291" s="187"/>
+      <c r="J291" s="187"/>
+      <c r="K291" s="187"/>
       <c r="L291" s="13"/>
     </row>
     <row r="292" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36931,17 +36931,17 @@
       <c r="B292" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C292" s="203" t="s">
+      <c r="C292" s="202" t="s">
         <v>719</v>
       </c>
-      <c r="D292" s="188"/>
-      <c r="E292" s="188"/>
-      <c r="F292" s="188"/>
-      <c r="G292" s="188"/>
-      <c r="H292" s="188"/>
-      <c r="I292" s="188"/>
-      <c r="J292" s="188"/>
-      <c r="K292" s="188"/>
+      <c r="D292" s="177"/>
+      <c r="E292" s="177"/>
+      <c r="F292" s="177"/>
+      <c r="G292" s="177"/>
+      <c r="H292" s="177"/>
+      <c r="I292" s="177"/>
+      <c r="J292" s="177"/>
+      <c r="K292" s="177"/>
       <c r="L292" s="13"/>
     </row>
     <row r="293" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36949,15 +36949,15 @@
       <c r="B293" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C293" s="186"/>
-      <c r="D293" s="177"/>
-      <c r="E293" s="177"/>
-      <c r="F293" s="177"/>
-      <c r="G293" s="177"/>
-      <c r="H293" s="177"/>
-      <c r="I293" s="177"/>
-      <c r="J293" s="177"/>
-      <c r="K293" s="177"/>
+      <c r="C293" s="174"/>
+      <c r="D293" s="175"/>
+      <c r="E293" s="175"/>
+      <c r="F293" s="175"/>
+      <c r="G293" s="175"/>
+      <c r="H293" s="175"/>
+      <c r="I293" s="175"/>
+      <c r="J293" s="175"/>
+      <c r="K293" s="175"/>
       <c r="L293" s="13"/>
     </row>
     <row r="294" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -36976,12 +36976,11 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="C288:K288"/>
-    <mergeCell ref="C289:K289"/>
-    <mergeCell ref="C290:K290"/>
-    <mergeCell ref="C291:K291"/>
-    <mergeCell ref="C293:K293"/>
-    <mergeCell ref="C292:K292"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C113:K113"/>
+    <mergeCell ref="C114:K114"/>
+    <mergeCell ref="C115:K115"/>
+    <mergeCell ref="C116:K116"/>
     <mergeCell ref="C118:K118"/>
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C121:K121"/>
@@ -36995,11 +36994,12 @@
     <mergeCell ref="C206:K206"/>
     <mergeCell ref="C117:K117"/>
     <mergeCell ref="C205:K205"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C113:K113"/>
-    <mergeCell ref="C114:K114"/>
-    <mergeCell ref="C115:K115"/>
-    <mergeCell ref="C116:K116"/>
+    <mergeCell ref="C288:K288"/>
+    <mergeCell ref="C289:K289"/>
+    <mergeCell ref="C290:K290"/>
+    <mergeCell ref="C291:K291"/>
+    <mergeCell ref="C293:K293"/>
+    <mergeCell ref="C292:K292"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -37024,20 +37024,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="181" t="s">
         <v>727</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -37113,17 +37113,17 @@
       <c r="B4" s="48" t="s">
         <v>304</v>
       </c>
-      <c r="C4" s="194" t="s">
+      <c r="C4" s="180" t="s">
         <v>305</v>
       </c>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="175"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="179"/>
+      <c r="I4" s="179"/>
+      <c r="J4" s="179"/>
+      <c r="K4" s="179"/>
       <c r="L4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="26.85" customHeight="1">
@@ -37131,17 +37131,17 @@
       <c r="B5" s="51" t="s">
         <v>728</v>
       </c>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="176" t="s">
         <v>729</v>
       </c>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="188"/>
-      <c r="K5" s="188"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
       <c r="L5" s="22"/>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -44371,20 +44371,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="181" t="s">
         <v>1498</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="1"/>
@@ -44460,17 +44460,17 @@
       <c r="B4" s="48" t="s">
         <v>304</v>
       </c>
-      <c r="C4" s="194" t="s">
+      <c r="C4" s="180" t="s">
         <v>305</v>
       </c>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="175"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="179"/>
+      <c r="H4" s="179"/>
+      <c r="I4" s="179"/>
+      <c r="J4" s="179"/>
+      <c r="K4" s="179"/>
       <c r="L4" s="49"/>
     </row>
     <row r="5" spans="1:12" ht="26.85" customHeight="1">
@@ -44478,17 +44478,17 @@
       <c r="B5" s="51" t="s">
         <v>1499</v>
       </c>
-      <c r="C5" s="192" t="s">
+      <c r="C5" s="176" t="s">
         <v>1500</v>
       </c>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-      <c r="I5" s="188"/>
-      <c r="J5" s="188"/>
-      <c r="K5" s="188"/>
+      <c r="D5" s="177"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="177"/>
+      <c r="G5" s="177"/>
+      <c r="H5" s="177"/>
+      <c r="I5" s="177"/>
+      <c r="J5" s="177"/>
+      <c r="K5" s="177"/>
       <c r="L5" s="22"/>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -46475,18 +46475,18 @@
       <c r="B87" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C87" s="184" t="str">
+      <c r="C87" s="182" t="str">
         <f t="array" ref="C87">IF(C88="","?",C88)&amp;IF(C89="","","; downloaded "&amp;C89)&amp;IF(C90="","","; "&amp;C90)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/migr_acq, https://data.statistik.gv.at/data/OGD_einbuergerungen_EINBJ_1.csv, https://www.statistik.at/fileadmin/pages/436/neu_Einbuergerungen.ods; downloaded 2026-05-20</v>
       </c>
-      <c r="D87" s="177"/>
-      <c r="E87" s="177"/>
-      <c r="F87" s="177"/>
-      <c r="G87" s="177"/>
-      <c r="H87" s="177"/>
-      <c r="I87" s="177"/>
-      <c r="J87" s="177"/>
-      <c r="K87" s="177"/>
+      <c r="D87" s="175"/>
+      <c r="E87" s="175"/>
+      <c r="F87" s="175"/>
+      <c r="G87" s="175"/>
+      <c r="H87" s="175"/>
+      <c r="I87" s="175"/>
+      <c r="J87" s="175"/>
+      <c r="K87" s="175"/>
       <c r="L87" s="13"/>
     </row>
     <row r="88" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -46494,17 +46494,17 @@
       <c r="B88" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C88" s="185" t="s">
+      <c r="C88" s="183" t="s">
         <v>1501</v>
       </c>
-      <c r="D88" s="177"/>
-      <c r="E88" s="177"/>
-      <c r="F88" s="177"/>
-      <c r="G88" s="177"/>
-      <c r="H88" s="177"/>
-      <c r="I88" s="177"/>
-      <c r="J88" s="177"/>
-      <c r="K88" s="177"/>
+      <c r="D88" s="175"/>
+      <c r="E88" s="175"/>
+      <c r="F88" s="175"/>
+      <c r="G88" s="175"/>
+      <c r="H88" s="175"/>
+      <c r="I88" s="175"/>
+      <c r="J88" s="175"/>
+      <c r="K88" s="175"/>
       <c r="L88" s="13"/>
     </row>
     <row r="89" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -46512,17 +46512,17 @@
       <c r="B89" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C89" s="185" t="s">
+      <c r="C89" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="D89" s="177"/>
-      <c r="E89" s="177"/>
-      <c r="F89" s="177"/>
-      <c r="G89" s="177"/>
-      <c r="H89" s="177"/>
-      <c r="I89" s="177"/>
-      <c r="J89" s="177"/>
-      <c r="K89" s="177"/>
+      <c r="D89" s="175"/>
+      <c r="E89" s="175"/>
+      <c r="F89" s="175"/>
+      <c r="G89" s="175"/>
+      <c r="H89" s="175"/>
+      <c r="I89" s="175"/>
+      <c r="J89" s="175"/>
+      <c r="K89" s="175"/>
       <c r="L89" s="13"/>
     </row>
     <row r="90" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -46531,14 +46531,14 @@
         <v>81</v>
       </c>
       <c r="C90" s="201"/>
-      <c r="D90" s="182"/>
-      <c r="E90" s="182"/>
-      <c r="F90" s="182"/>
-      <c r="G90" s="182"/>
-      <c r="H90" s="182"/>
-      <c r="I90" s="182"/>
-      <c r="J90" s="182"/>
-      <c r="K90" s="182"/>
+      <c r="D90" s="187"/>
+      <c r="E90" s="187"/>
+      <c r="F90" s="187"/>
+      <c r="G90" s="187"/>
+      <c r="H90" s="187"/>
+      <c r="I90" s="187"/>
+      <c r="J90" s="187"/>
+      <c r="K90" s="187"/>
       <c r="L90" s="13"/>
     </row>
     <row r="91" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -46546,17 +46546,17 @@
       <c r="B91" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C91" s="203" t="s">
+      <c r="C91" s="202" t="s">
         <v>1502</v>
       </c>
-      <c r="D91" s="188"/>
-      <c r="E91" s="188"/>
-      <c r="F91" s="188"/>
-      <c r="G91" s="188"/>
-      <c r="H91" s="188"/>
-      <c r="I91" s="188"/>
-      <c r="J91" s="188"/>
-      <c r="K91" s="188"/>
+      <c r="D91" s="177"/>
+      <c r="E91" s="177"/>
+      <c r="F91" s="177"/>
+      <c r="G91" s="177"/>
+      <c r="H91" s="177"/>
+      <c r="I91" s="177"/>
+      <c r="J91" s="177"/>
+      <c r="K91" s="177"/>
       <c r="L91" s="13"/>
     </row>
     <row r="92" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -46564,15 +46564,15 @@
       <c r="B92" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C92" s="186"/>
-      <c r="D92" s="177"/>
-      <c r="E92" s="177"/>
-      <c r="F92" s="177"/>
-      <c r="G92" s="177"/>
-      <c r="H92" s="177"/>
-      <c r="I92" s="177"/>
-      <c r="J92" s="177"/>
-      <c r="K92" s="177"/>
+      <c r="C92" s="174"/>
+      <c r="D92" s="175"/>
+      <c r="E92" s="175"/>
+      <c r="F92" s="175"/>
+      <c r="G92" s="175"/>
+      <c r="H92" s="175"/>
+      <c r="I92" s="175"/>
+      <c r="J92" s="175"/>
+      <c r="K92" s="175"/>
       <c r="L92" s="13"/>
     </row>
     <row r="93" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -46597,14 +46597,14 @@
       <c r="C94" s="205" t="s">
         <v>1504</v>
       </c>
-      <c r="D94" s="182"/>
-      <c r="E94" s="182"/>
-      <c r="F94" s="182"/>
-      <c r="G94" s="182"/>
-      <c r="H94" s="182"/>
-      <c r="I94" s="182"/>
-      <c r="J94" s="182"/>
-      <c r="K94" s="182"/>
+      <c r="D94" s="187"/>
+      <c r="E94" s="187"/>
+      <c r="F94" s="187"/>
+      <c r="G94" s="187"/>
+      <c r="H94" s="187"/>
+      <c r="I94" s="187"/>
+      <c r="J94" s="187"/>
+      <c r="K94" s="187"/>
       <c r="L94" s="22"/>
     </row>
     <row r="95" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -48414,18 +48414,18 @@
       <c r="B174" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="C174" s="184" t="str">
+      <c r="C174" s="182" t="str">
         <f t="array" ref="C174">IF(C175="","?",C175)&amp;IF(C176="","","; downloaded "&amp;C176)&amp;IF(C177="","","; "&amp;C177)</f>
         <v>https://ec.europa.eu/eurostat/databrowser/view/migr_acq, https://data.statistik.gv.at/data/OGD_einbuergerungen_EINBJ_1.csv, https://www.statistik.at/fileadmin/pages/436/neu_Einbuergerungen.ods; downloaded 2026-05-20</v>
       </c>
-      <c r="D174" s="177"/>
-      <c r="E174" s="177"/>
-      <c r="F174" s="177"/>
-      <c r="G174" s="177"/>
-      <c r="H174" s="177"/>
-      <c r="I174" s="177"/>
-      <c r="J174" s="177"/>
-      <c r="K174" s="177"/>
+      <c r="D174" s="175"/>
+      <c r="E174" s="175"/>
+      <c r="F174" s="175"/>
+      <c r="G174" s="175"/>
+      <c r="H174" s="175"/>
+      <c r="I174" s="175"/>
+      <c r="J174" s="175"/>
+      <c r="K174" s="175"/>
       <c r="L174" s="13"/>
     </row>
     <row r="175" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -48433,17 +48433,17 @@
       <c r="B175" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C175" s="185" t="s">
+      <c r="C175" s="183" t="s">
         <v>1501</v>
       </c>
-      <c r="D175" s="177"/>
-      <c r="E175" s="177"/>
-      <c r="F175" s="177"/>
-      <c r="G175" s="177"/>
-      <c r="H175" s="177"/>
-      <c r="I175" s="177"/>
-      <c r="J175" s="177"/>
-      <c r="K175" s="177"/>
+      <c r="D175" s="175"/>
+      <c r="E175" s="175"/>
+      <c r="F175" s="175"/>
+      <c r="G175" s="175"/>
+      <c r="H175" s="175"/>
+      <c r="I175" s="175"/>
+      <c r="J175" s="175"/>
+      <c r="K175" s="175"/>
       <c r="L175" s="13"/>
     </row>
     <row r="176" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -48451,17 +48451,17 @@
       <c r="B176" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C176" s="185" t="s">
+      <c r="C176" s="183" t="s">
         <v>80</v>
       </c>
-      <c r="D176" s="177"/>
-      <c r="E176" s="177"/>
-      <c r="F176" s="177"/>
-      <c r="G176" s="177"/>
-      <c r="H176" s="177"/>
-      <c r="I176" s="177"/>
-      <c r="J176" s="177"/>
-      <c r="K176" s="177"/>
+      <c r="D176" s="175"/>
+      <c r="E176" s="175"/>
+      <c r="F176" s="175"/>
+      <c r="G176" s="175"/>
+      <c r="H176" s="175"/>
+      <c r="I176" s="175"/>
+      <c r="J176" s="175"/>
+      <c r="K176" s="175"/>
       <c r="L176" s="13"/>
     </row>
     <row r="177" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -48470,14 +48470,14 @@
         <v>81</v>
       </c>
       <c r="C177" s="201"/>
-      <c r="D177" s="182"/>
-      <c r="E177" s="182"/>
-      <c r="F177" s="182"/>
-      <c r="G177" s="182"/>
-      <c r="H177" s="182"/>
-      <c r="I177" s="182"/>
-      <c r="J177" s="182"/>
-      <c r="K177" s="182"/>
+      <c r="D177" s="187"/>
+      <c r="E177" s="187"/>
+      <c r="F177" s="187"/>
+      <c r="G177" s="187"/>
+      <c r="H177" s="187"/>
+      <c r="I177" s="187"/>
+      <c r="J177" s="187"/>
+      <c r="K177" s="187"/>
       <c r="L177" s="13"/>
     </row>
     <row r="178" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -48485,17 +48485,17 @@
       <c r="B178" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C178" s="203" t="s">
+      <c r="C178" s="202" t="s">
         <v>1505</v>
       </c>
-      <c r="D178" s="188"/>
-      <c r="E178" s="188"/>
-      <c r="F178" s="188"/>
-      <c r="G178" s="188"/>
-      <c r="H178" s="188"/>
-      <c r="I178" s="188"/>
-      <c r="J178" s="188"/>
-      <c r="K178" s="188"/>
+      <c r="D178" s="177"/>
+      <c r="E178" s="177"/>
+      <c r="F178" s="177"/>
+      <c r="G178" s="177"/>
+      <c r="H178" s="177"/>
+      <c r="I178" s="177"/>
+      <c r="J178" s="177"/>
+      <c r="K178" s="177"/>
       <c r="L178" s="13"/>
     </row>
     <row r="179" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -48503,15 +48503,15 @@
       <c r="B179" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C179" s="186"/>
-      <c r="D179" s="177"/>
-      <c r="E179" s="177"/>
-      <c r="F179" s="177"/>
-      <c r="G179" s="177"/>
-      <c r="H179" s="177"/>
-      <c r="I179" s="177"/>
-      <c r="J179" s="177"/>
-      <c r="K179" s="177"/>
+      <c r="C179" s="174"/>
+      <c r="D179" s="175"/>
+      <c r="E179" s="175"/>
+      <c r="F179" s="175"/>
+      <c r="G179" s="175"/>
+      <c r="H179" s="175"/>
+      <c r="I179" s="175"/>
+      <c r="J179" s="175"/>
+      <c r="K179" s="175"/>
       <c r="L179" s="13"/>
     </row>
     <row r="180" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -48530,12 +48530,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C174:K174"/>
-    <mergeCell ref="C175:K175"/>
-    <mergeCell ref="C176:K176"/>
-    <mergeCell ref="C177:K177"/>
-    <mergeCell ref="C179:K179"/>
-    <mergeCell ref="C178:K178"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="C94:K94"/>
     <mergeCell ref="C87:K87"/>
@@ -48546,6 +48540,12 @@
     <mergeCell ref="C91:K91"/>
     <mergeCell ref="C5:K5"/>
     <mergeCell ref="C4:K4"/>
+    <mergeCell ref="C174:K174"/>
+    <mergeCell ref="C175:K175"/>
+    <mergeCell ref="C176:K176"/>
+    <mergeCell ref="C177:K177"/>
+    <mergeCell ref="C179:K179"/>
+    <mergeCell ref="C178:K178"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>
@@ -48570,20 +48570,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="27.6" customHeight="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="181" t="s">
         <v>1506</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
     </row>
     <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1">
       <c r="A2" s="156"/>
@@ -48677,15 +48677,15 @@
       <c r="B5" s="21" t="s">
         <v>1508</v>
       </c>
-      <c r="C5" s="178"/>
-      <c r="D5" s="177"/>
-      <c r="E5" s="177"/>
-      <c r="F5" s="177"/>
-      <c r="G5" s="177"/>
-      <c r="H5" s="177"/>
-      <c r="I5" s="177"/>
-      <c r="J5" s="177"/>
-      <c r="K5" s="177"/>
+      <c r="C5" s="190"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="175"/>
+      <c r="G5" s="175"/>
+      <c r="H5" s="175"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="175"/>
       <c r="L5" s="22"/>
     </row>
     <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -48851,15 +48851,15 @@
       <c r="B13" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="178"/>
-      <c r="D13" s="177"/>
-      <c r="E13" s="177"/>
-      <c r="F13" s="177"/>
-      <c r="G13" s="177"/>
-      <c r="H13" s="177"/>
-      <c r="I13" s="177"/>
-      <c r="J13" s="177"/>
-      <c r="K13" s="177"/>
+      <c r="C13" s="190"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="175"/>
+      <c r="F13" s="175"/>
+      <c r="G13" s="175"/>
+      <c r="H13" s="175"/>
+      <c r="I13" s="175"/>
+      <c r="J13" s="175"/>
+      <c r="K13" s="175"/>
       <c r="L13" s="22"/>
     </row>
     <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -53365,15 +53365,15 @@
       <c r="B118" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="C118" s="178"/>
-      <c r="D118" s="177"/>
-      <c r="E118" s="177"/>
-      <c r="F118" s="177"/>
-      <c r="G118" s="177"/>
-      <c r="H118" s="177"/>
-      <c r="I118" s="177"/>
-      <c r="J118" s="177"/>
-      <c r="K118" s="177"/>
+      <c r="C118" s="190"/>
+      <c r="D118" s="175"/>
+      <c r="E118" s="175"/>
+      <c r="F118" s="175"/>
+      <c r="G118" s="175"/>
+      <c r="H118" s="175"/>
+      <c r="I118" s="175"/>
+      <c r="J118" s="175"/>
+      <c r="K118" s="175"/>
       <c r="L118" s="22"/>
     </row>
     <row r="119" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -55086,15 +55086,15 @@
       <c r="B160" s="21" t="s">
         <v>403</v>
       </c>
-      <c r="C160" s="178"/>
-      <c r="D160" s="177"/>
-      <c r="E160" s="177"/>
-      <c r="F160" s="177"/>
-      <c r="G160" s="177"/>
-      <c r="H160" s="177"/>
-      <c r="I160" s="177"/>
-      <c r="J160" s="177"/>
-      <c r="K160" s="177"/>
+      <c r="C160" s="190"/>
+      <c r="D160" s="175"/>
+      <c r="E160" s="175"/>
+      <c r="F160" s="175"/>
+      <c r="G160" s="175"/>
+      <c r="H160" s="175"/>
+      <c r="I160" s="175"/>
+      <c r="J160" s="175"/>
+      <c r="K160" s="175"/>
       <c r="L160" s="22"/>
     </row>
     <row r="161" spans="1:12" ht="20.100000000000001" customHeight="1">
@@ -59580,15 +59580,15 @@
       <c r="B264" s="21" t="s">
         <v>611</v>
       </c>
-      <c r="C264" s="178"/>
-      <c r="D264" s="177"/>
-      <c r="E264" s="177"/>
-      <c r="F264" s="177"/>
-      <c r="G264" s="177"/>
-      <c r="H264" s="177"/>
-      <c r="I264" s="177"/>
-      <c r="J264" s="177"/>
-      <c r="K264" s="177"/>
+      <c r="C264" s="190"/>
+      <c r="D264" s="175"/>
+      <c r="E264" s="175"/>
+      <c r="F264" s="175"/>
+      <c r="G264" s="175"/>
+      <c r="H264" s="175"/>
+      <c r="I264" s="175"/>
+      <c r="J264" s="175"/>
+      <c r="K264" s="175"/>
       <c r="L264" s="22"/>
     </row>
     <row r="265" spans="1:12" ht="20.100000000000001" customHeight="1">
